--- a/data/reports/MASTER_FINAL_REPORT.xlsx
+++ b/data/reports/MASTER_FINAL_REPORT.xlsx
@@ -551,22 +551,22 @@
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I2" t="n">
         <v>357</v>
       </c>
       <c r="J2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -581,13 +581,13 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005018820577164366</v>
+        <v>0.006265664160401002</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9786476868327402</v>
+        <v>0.9798339264531435</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="R2" t="n">
         <v>0.9571045576407506</v>
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8265143680744562</v>
+        <v>0.8236642649555947</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>1655</v>
+        <v>1603</v>
       </c>
       <c r="H3" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="J3" t="n">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -644,38 +644,38 @@
         <v>46165</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006273525721455458</v>
+        <v>0.008145363408521303</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9816132858837485</v>
+        <v>0.9507710557532622</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8378378378378378</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9812332439678284</v>
+        <v>0.9222520107238605</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8322981366459627</v>
+        <v>0.2530864197530864</v>
       </c>
       <c r="T3" t="n">
-        <v>0.65661122675386</v>
+        <v>0.6891056586967521</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>138, 183, 318, 381, 813, 831</t>
+          <t>123, 132, 213, 231, 312, 321</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>349</v>
+        <v>49</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -683,68 +683,68 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v>69</v>
-      </c>
       <c r="G4" t="n">
-        <v>1633</v>
+        <v>1574</v>
       </c>
       <c r="H4" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I4" t="n">
-        <v>336</v>
+        <v>291</v>
       </c>
       <c r="J4" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46136</v>
+        <v>46171</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04328732747804266</v>
+        <v>0.0006265664160401002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.968564650059312</v>
+        <v>0.933570581257414</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.900804289544236</v>
+        <v>0.7801608579088471</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6894409937888198</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6518700284362716</v>
+        <v>0.6752954725022486</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>349, 394, 439, 493, 934, 943</t>
+          <t>049, 094, 409, 490, 904, 940</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -752,68 +752,68 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>1603</v>
+        <v>1557</v>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I5" t="n">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="J5" t="n">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46165</v>
+        <v>46156</v>
       </c>
       <c r="M5" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006900878293601004</v>
+        <v>0.01879699248120301</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9507710557532622</v>
+        <v>0.9234875444839857</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9222520107238605</v>
+        <v>0.8310991957104558</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2546583850931677</v>
+        <v>0.7345679012345679</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6491026893016233</v>
+        <v>0.6745821605993164</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>123, 132, 213, 231, 312, 321</t>
+          <t>078, 087, 708, 780, 807, 870</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -821,68 +821,68 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>1554</v>
+        <v>1587</v>
       </c>
       <c r="H6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="J6" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="M6" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01756587202007528</v>
+        <v>0.003759398496240601</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9217081850533808</v>
+        <v>0.9412811387900356</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8284182305630027</v>
+        <v>0.8820375335120644</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="T6" t="n">
-        <v>0.644374764515547</v>
+        <v>0.6733843013005862</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>078, 087, 708, 780, 807, 870</t>
+          <t>037, 073, 307, 370, 703, 730</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>37</v>
+        <v>345</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -890,68 +890,68 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>1584</v>
+        <v>1630</v>
       </c>
       <c r="H7" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I7" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J7" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46168</v>
+        <v>46144</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002509410288582183</v>
+        <v>0.03446115288220551</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9395017793594306</v>
+        <v>0.966785290628707</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.7477477477477478</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8793565683646113</v>
+        <v>0.8739946380697051</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7577639751552795</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6431798261475448</v>
+        <v>0.6677511087969386</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>037, 073, 307, 370, 703, 730</t>
+          <t>345, 354, 435, 453, 534, 543</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>345</v>
+        <v>138</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -962,22 +962,22 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>1628</v>
+        <v>1655</v>
       </c>
       <c r="H8" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>326</v>
+        <v>366</v>
       </c>
       <c r="J8" t="n">
         <v>134</v>
@@ -986,41 +986,41 @@
         <v>1</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46144</v>
+        <v>46165</v>
       </c>
       <c r="M8" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03324968632371392</v>
+        <v>0.007518796992481203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9655990510083037</v>
+        <v>0.9816132858837485</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8739946380697051</v>
+        <v>0.9812332439678284</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8322981366459627</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6406632004102514</v>
+        <v>0.6662858800483185</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>345, 354, 435, 453, 534, 543</t>
+          <t>138, 183, 318, 381, 813, 831</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>158</v>
+        <v>349</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1028,62 +1028,62 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>1602</v>
+        <v>1636</v>
       </c>
       <c r="H9" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J9" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02697616060225847</v>
+        <v>0.04448621553884712</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9501779359430605</v>
+        <v>0.9703440094899169</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8981481481481481</v>
+        <v>0.8378378378378378</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8981233243967829</v>
+        <v>0.9034852546916891</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8322981366459627</v>
+        <v>0.6851851851851852</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6382195554289978</v>
+        <v>0.6660869249062118</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>158, 185, 518, 581, 815, 851</t>
+          <t>349, 394, 439, 493, 934, 943</t>
         </is>
       </c>
     </row>
@@ -1106,10 +1106,10 @@
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H10" t="n">
         <v>98</v>
@@ -1130,25 +1130,25 @@
         <v>0.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01631116687578419</v>
+        <v>0.01754385964912281</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9495848161328588</v>
+        <v>0.9501779359430605</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.8828828828828829</v>
       </c>
       <c r="R10" t="n">
         <v>0.8579088471849866</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6335403726708074</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="T10" t="n">
-        <v>0.636492635741997</v>
+        <v>0.6641125868269147</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
         <v>1556</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I11" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J11" t="n">
         <v>134</v>
@@ -1193,41 +1193,41 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46152</v>
+        <v>46140</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02258469259723965</v>
+        <v>0.03947368421052631</v>
       </c>
       <c r="P11" t="n">
         <v>0.9228944246737841</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8828828828828829</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8739946380697051</v>
+        <v>0.8659517426273459</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8322981366459627</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6291959147755586</v>
+        <v>0.654665346459657</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>239, 293, 329, 392, 923, 932</t>
+          <t>129, 192, 219, 291, 912, 921</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129</v>
+        <v>389</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1235,68 +1235,68 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>1555</v>
+        <v>1609</v>
       </c>
       <c r="H12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I12" t="n">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="J12" t="n">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="M12" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0382685069008783</v>
+        <v>0.0137844611528822</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9223013048635824</v>
+        <v>0.9543297746144721</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9099099099099099</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8659517426273459</v>
+        <v>0.839142091152815</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8322981366459627</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6280367936091</v>
+        <v>0.6519805867273162</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>129, 192, 219, 291, 912, 921</t>
+          <t>389, 398, 839, 893, 938, 983</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>389</v>
+        <v>156</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1304,68 +1304,68 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1608</v>
+        <v>1595</v>
       </c>
       <c r="H13" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="I13" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J13" t="n">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="M13" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01254705144291092</v>
+        <v>0.0012531328320802</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9537366548042705</v>
+        <v>0.9460260972716489</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="R13" t="n">
-        <v>0.839142091152815</v>
+        <v>0.8310991957104558</v>
       </c>
       <c r="S13" t="n">
-        <v>0.391304347826087</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6252861648977056</v>
+        <v>0.6506365095727513</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>389, 398, 839, 893, 938, 983</t>
+          <t>156, 165, 516, 561, 615, 651</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>1595</v>
+        <v>1602</v>
       </c>
       <c r="H14" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I14" t="n">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="J14" t="n">
         <v>134</v>
@@ -1400,41 +1400,41 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46170</v>
+        <v>46149</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.02819548872180451</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9460260972716489</v>
+        <v>0.9501779359430605</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.8468468468468469</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8310991957104558</v>
+        <v>0.8981233243967829</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8322981366459627</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6248345509180085</v>
+        <v>0.6480154423758594</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>156, 165, 516, 561, 615, 651</t>
+          <t>158, 185, 518, 581, 815, 851</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>468</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1442,68 +1442,68 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>1614</v>
+        <v>1570</v>
       </c>
       <c r="H15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I15" t="n">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="J15" t="n">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46158</v>
+        <v>46148</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01568381430363865</v>
+        <v>0.02944862155388471</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9572953736654805</v>
+        <v>0.9311981020166074</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7870370370370371</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="R15" t="n">
-        <v>0.935656836461126</v>
+        <v>0.868632707774799</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6335403726708074</v>
+        <v>0.2530864197530864</v>
       </c>
       <c r="T15" t="n">
-        <v>0.622103172265126</v>
+        <v>0.6461126330476603</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>468, 486, 648, 684, 846, 864</t>
+          <t>015, 051, 105, 150, 501, 510</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>238</v>
+        <v>149</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1511,68 +1511,68 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>1574</v>
+        <v>1635</v>
       </c>
       <c r="H16" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I16" t="n">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="J16" t="n">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46133</v>
+        <v>46154</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04642409033877039</v>
+        <v>0.02192982456140351</v>
       </c>
       <c r="P16" t="n">
-        <v>0.933570581257414</v>
+        <v>0.9697508896797153</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8873994638069705</v>
+        <v>0.9034852546916891</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6218845256090103</v>
+        <v>0.6424218976209686</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>238, 283, 328, 382, 823, 832</t>
+          <t>149, 194, 419, 491, 914, 941</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>469</v>
+        <v>239</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
         <v>16</v>
@@ -1589,59 +1589,59 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>1596</v>
+        <v>1557</v>
       </c>
       <c r="H17" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I17" t="n">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="J17" t="n">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="M17" t="n">
         <v>0.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06085319949811794</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9466192170818505</v>
+        <v>0.9234875444839857</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8148148148148148</v>
+        <v>0.8558558558558559</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8927613941018767</v>
+        <v>0.8739946380697051</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5403726708074534</v>
+        <v>0.8271604938271605</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6190689944533125</v>
+        <v>0.6409024907865861</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>469, 496, 649, 694, 946, 964</t>
+          <t>239, 293, 329, 392, 923, 932</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>468</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1649,68 +1649,68 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>1568</v>
+        <v>1616</v>
       </c>
       <c r="H18" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I18" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="J18" t="n">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46148</v>
+        <v>46158</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02823086574654956</v>
+        <v>0.01691729323308271</v>
       </c>
       <c r="P18" t="n">
-        <v>0.930011862396204</v>
+        <v>0.9584816132858838</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7657657657657657</v>
       </c>
       <c r="R18" t="n">
-        <v>0.868632707774799</v>
+        <v>0.935656836461126</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2546583850931677</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6180196715738847</v>
+        <v>0.6351316033722131</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>015, 051, 105, 150, 501, 510</t>
+          <t>468, 486, 648, 684, 846, 864</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>568</v>
+        <v>469</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1721,22 +1721,22 @@
         <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G19" t="n">
-        <v>1566</v>
+        <v>1599</v>
       </c>
       <c r="H19" t="n">
         <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="J19" t="n">
         <v>87</v>
@@ -1745,35 +1745,35 @@
         <v>1</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46134</v>
+        <v>46122</v>
       </c>
       <c r="M19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04579673776662484</v>
+        <v>0.06203007518796992</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9288256227758007</v>
+        <v>0.9483985765124555</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8310991957104558</v>
+        <v>0.8954423592493298</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5403726708074534</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6169219440838802</v>
+        <v>0.6343295988102717</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>568, 586, 658, 685, 856, 865</t>
+          <t>469, 496, 649, 694, 946, 964</t>
         </is>
       </c>
     </row>
@@ -1796,19 +1796,19 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="H20" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I20" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J20" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1820,25 +1820,25 @@
         <v>0.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O20" t="n">
-        <v>0.02948557089084065</v>
+        <v>0.03070175438596491</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9175563463819691</v>
+        <v>0.9193357058125742</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="R20" t="n">
-        <v>0.871313672922252</v>
+        <v>0.8739946380697051</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6163555528432174</v>
+        <v>0.6327898360604893</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>149</v>
+        <v>238</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1856,68 +1856,68 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" t="n">
         <v>14</v>
       </c>
-      <c r="D21" t="n">
-        <v>9</v>
-      </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G21" t="n">
-        <v>1632</v>
+        <v>1574</v>
       </c>
       <c r="H21" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J21" t="n">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46154</v>
+        <v>46133</v>
       </c>
       <c r="M21" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02070263488080301</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9679715302491103</v>
+        <v>0.933570581257414</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8796296296296297</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="R21" t="n">
-        <v>0.900804289544236</v>
+        <v>0.8873994638069705</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8322981366459627</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6133199226938925</v>
+        <v>0.6320337391710218</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>149, 194, 419, 491, 914, 941</t>
+          <t>238, 283, 328, 382, 823, 832</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134</v>
+        <v>459</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1925,68 +1925,68 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>632</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
-        <v>1680</v>
+        <v>1583</v>
       </c>
       <c r="H22" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I22" t="n">
-        <v>373</v>
+        <v>308</v>
       </c>
       <c r="J22" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>45853</v>
+        <v>46149</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O22" t="n">
-        <v>0.396486825595985</v>
+        <v>0.02756892230576441</v>
       </c>
       <c r="P22" t="n">
-        <v>0.99644128113879</v>
+        <v>0.938908659549229</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.7927927927927928</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0.8257372654155496</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4720496894409938</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6077624728560632</v>
+        <v>0.6302039012558499</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>134, 143, 314, 341, 413, 431</t>
+          <t>459, 495, 549, 594, 945, 954</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135</v>
+        <v>568</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1994,62 +1994,62 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G23" t="n">
-        <v>1632</v>
+        <v>1566</v>
       </c>
       <c r="H23" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I23" t="n">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="J23" t="n">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>46147</v>
+        <v>46134</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02885821831869511</v>
+        <v>0.04699248120300752</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9679715302491103</v>
+        <v>0.9288256227758007</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.8981481481481481</v>
+        <v>0.7927927927927928</v>
       </c>
       <c r="R23" t="n">
-        <v>0.868632707774799</v>
+        <v>0.8310991957104558</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6211180124223602</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6060103685848324</v>
+        <v>0.6278804698567628</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>135, 153, 315, 351, 513, 531</t>
+          <t>568, 586, 658, 685, 856, 865</t>
         </is>
       </c>
     </row>
@@ -2072,16 +2072,16 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J24" t="n">
         <v>122</v>
@@ -2096,25 +2096,25 @@
         <v>0.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.003136762860727729</v>
+        <v>0.004385964912280702</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9371293001186239</v>
+        <v>0.9395017793594306</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8766756032171582</v>
+        <v>0.8820375335120644</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7577639751552795</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6055026001304986</v>
+        <v>0.6224183651318967</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>189</v>
+        <v>289</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2132,68 +2132,68 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>527</v>
+        <v>90</v>
       </c>
       <c r="G25" t="n">
-        <v>1607</v>
+        <v>1527</v>
       </c>
       <c r="H25" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I25" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="J25" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>45906</v>
+        <v>46126</v>
       </c>
       <c r="M25" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3306148055207027</v>
+        <v>0.05639097744360902</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9531435349940688</v>
+        <v>0.905693950177936</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9722222222222222</v>
+        <v>0.8558558558558559</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8847184986595175</v>
+        <v>0.8042895442359249</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6335403726708074</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6046393313819652</v>
+        <v>0.6183366687142786</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>189, 198, 819, 891, 918, 981</t>
+          <t>289, 298, 829, 892, 928, 982</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>346</v>
+        <v>135</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2201,62 +2201,62 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>460</v>
+        <v>48</v>
       </c>
       <c r="G26" t="n">
-        <v>1644</v>
+        <v>1632</v>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I26" t="n">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="J26" t="n">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>45939</v>
+        <v>46147</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2885821831869511</v>
+        <v>0.03007518796992481</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9750889679715302</v>
+        <v>0.9679715302491103</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7870370370370371</v>
+        <v>0.8468468468468469</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9731903485254692</v>
+        <v>0.868632707774799</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="T26" t="n">
-        <v>0.604482038976581</v>
+        <v>0.6158710808121329</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>346, 364, 436, 463, 634, 643</t>
+          <t>135, 153, 315, 351, 513, 531</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>139</v>
       </c>
       <c r="B2" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" t="n">
         <v>25</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>52.35</v>
+        <v>51.95</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2338,38 +2338,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>138, 183, 318, 381, 813, 831</t>
+          <t>179, 197, 719, 791, 917, 971</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>179</v>
+        <v>379</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -2378,395 +2378,395 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>179, 197, 719, 791, 917, 971</t>
+          <t>379, 397, 739, 793, 937, 973</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>50.8</v>
+        <v>50.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>189, 198, 819, 891, 918, 981</t>
+          <t>199, 919, 991</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>379</v>
+        <v>177</v>
       </c>
       <c r="B6" t="n">
         <v>101</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>50.4</v>
+        <v>50.75</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>379, 397, 739, 793, 937, 973</t>
+          <t>177, 717, 771</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>177</v>
+        <v>399</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>50.35</v>
+        <v>50.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>177, 717, 771</t>
+          <t>399, 939, 993</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>50.35</v>
+        <v>50.25</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>199, 919, 991</t>
+          <t>138, 183, 318, 381, 813, 831</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>129, 192, 219, 291, 912, 921</t>
+          <t>137, 173, 317, 371, 713, 731</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>50.3</v>
+        <v>50.05</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>137, 173, 317, 371, 713, 731</t>
+          <t>189, 198, 819, 891, 918, 981</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>389</v>
+        <v>129</v>
       </c>
       <c r="B11" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>50.1</v>
+        <v>49.9</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>389, 398, 839, 893, 938, 983</t>
+          <t>129, 192, 219, 291, 912, 921</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="B12" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>49.85</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>399, 939, 993</t>
+          <t>369, 396, 639, 693, 936, 963</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>49.85</v>
+        <v>49.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>369, 396, 639, 693, 936, 963</t>
+          <t>389, 398, 839, 893, 938, 983</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>378</v>
+        <v>299</v>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C14" t="n">
         <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>378, 387, 738, 783, 837, 873</t>
+          <t>299, 929, 992</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>178</v>
+        <v>378</v>
       </c>
       <c r="B15" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>178, 187, 718, 781, 817, 871</t>
+          <t>378, 387, 738, 783, 837, 873</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>339</v>
+        <v>119</v>
       </c>
       <c r="B16" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>49.65</v>
+        <v>49.35</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>339, 393, 933</t>
+          <t>119, 191, 911</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>159</v>
+        <v>699</v>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>49.25</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>159, 195, 519, 591, 915, 951</t>
+          <t>699, 969, 996</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113</v>
+        <v>339</v>
       </c>
       <c r="B18" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>49.6</v>
+        <v>49.25</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>113, 131, 311</t>
+          <t>339, 393, 933</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B19" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>158, 185, 518, 581, 815, 851</t>
+          <t>159, 195, 519, 591, 915, 951</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119</v>
+        <v>799</v>
       </c>
       <c r="B20" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" t="n">
         <v>17</v>
@@ -2775,39 +2775,39 @@
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>49.55</v>
+        <v>49.2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>119, 191, 911</t>
+          <t>799, 979, 997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="B21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>49.5</v>
+        <v>48.95</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>239, 293, 329, 392, 923, 932</t>
+          <t>178, 187, 718, 781, 817, 871</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
         <v>117</v>
       </c>
       <c r="B22" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>49.35</v>
+        <v>48.95</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2838,88 +2838,88 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="B23" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>49.2</v>
+        <v>48.75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>299, 929, 992</t>
+          <t>239, 293, 329, 392, 923, 932</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="B24" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>49.15</v>
+        <v>48.65</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>118, 181, 811</t>
+          <t>169, 196, 619, 691, 916, 961</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B25" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
       <c r="F25" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>135, 153, 315, 351, 513, 531</t>
+          <t>149, 194, 419, 491, 914, 941</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>169</v>
+        <v>377</v>
       </c>
       <c r="B26" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D26" t="n">
         <v>6</v>
@@ -2928,11 +2928,11 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>48.65</v>
+        <v>48.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>169, 196, 619, 691, 916, 961</t>
+          <t>377, 737, 773</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5">
@@ -3007,7 +3007,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -3015,7 +3015,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9">
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
@@ -3158,7 +3158,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
         <v>112</v>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -3182,7 +3182,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B16" t="n">
         <v>111</v>
@@ -3222,15 +3222,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B21" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B22" t="n">
         <v>105</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B23" t="n">
         <v>105</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B25" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
@@ -3374,7 +3374,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="B40" t="n">
         <v>93</v>
@@ -3385,15 +3385,15 @@
         <v>9</v>
       </c>
       <c r="B41" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="B42" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
@@ -3539,7 +3539,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
@@ -3595,7 +3595,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -3810,7 +3810,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>9</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B6" t="n">
         <v>9</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
         <v>9</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" t="n">
         <v>9</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B9" t="n">
         <v>9</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>9</v>
@@ -3866,15 +3866,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B13" t="n">
         <v>8</v>
@@ -3882,15 +3882,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="B15" t="n">
         <v>7</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>7</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B17" t="n">
         <v>7</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="B19" t="n">
         <v>7</v>
@@ -3930,23 +3930,23 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B22" t="n">
         <v>6</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
@@ -3970,7 +3970,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B33" t="n">
         <v>5</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" t="n">
         <v>5</v>
@@ -4050,15 +4050,15 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="B39" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B41" t="n">
         <v>4</v>
@@ -4106,15 +4106,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="B43" t="n">
         <v>3</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B44" t="n">
         <v>3</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B45" t="n">
         <v>3</v>
@@ -4138,7 +4138,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B46" t="n">
         <v>3</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="B47" t="n">
         <v>3</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="B48" t="n">
         <v>3</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B49" t="n">
         <v>3</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4262,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="D3" t="n">
         <v>140</v>
@@ -4302,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -4362,7 +4362,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
@@ -4382,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D9" t="n">
         <v>534</v>
@@ -4422,7 +4422,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D10" t="n">
         <v>341</v>
@@ -4442,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -4462,7 +4462,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D12" t="n">
         <v>158.25</v>
@@ -4482,7 +4482,7 @@
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D13" t="n">
         <v>130.5</v>
@@ -4502,7 +4502,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D15" t="n">
         <v>87.75</v>
@@ -4542,7 +4542,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D16" t="n">
         <v>313.67</v>
@@ -4562,7 +4562,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D17" t="n">
         <v>189</v>
@@ -4582,7 +4582,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D18" t="n">
         <v>441</v>
@@ -4602,7 +4602,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D19" t="n">
         <v>479</v>
@@ -4616,59 +4616,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="D20" t="n">
-        <v>169.17</v>
+        <v>297.33</v>
       </c>
       <c r="E20" t="n">
-        <v>315</v>
+        <v>451</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45827</v>
+        <v>45832</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D21" t="n">
-        <v>297.33</v>
+        <v>260</v>
       </c>
       <c r="E21" t="n">
-        <v>451</v>
+        <v>381</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45832</v>
+        <v>45836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D22" t="n">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="E22" t="n">
-        <v>381</v>
+        <v>462</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>45836</v>
@@ -4676,259 +4676,259 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>779</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D23" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E23" t="n">
-        <v>462</v>
+        <v>588</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>45836</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>779</v>
+        <v>134</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="D24" t="n">
-        <v>227</v>
+        <v>92.36</v>
       </c>
       <c r="E24" t="n">
-        <v>588</v>
+        <v>259</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>45840</v>
+        <v>45853</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134</v>
+        <v>477</v>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="D25" t="n">
-        <v>92.36</v>
+        <v>432</v>
       </c>
       <c r="E25" t="n">
-        <v>259</v>
+        <v>542</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>45853</v>
+        <v>45865</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>477</v>
+        <v>256</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="D26" t="n">
-        <v>432</v>
+        <v>128.11</v>
       </c>
       <c r="E26" t="n">
-        <v>542</v>
+        <v>200</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>45865</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="D27" t="n">
-        <v>128.11</v>
+        <v>194.83</v>
       </c>
       <c r="E27" t="n">
-        <v>200</v>
+        <v>291</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>45869</v>
+        <v>45883</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128</v>
+        <v>899</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="D28" t="n">
-        <v>194.83</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45883</v>
+        <v>45890</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>899</v>
+        <v>667</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>45890</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>667</v>
+        <v>8</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D30" t="n">
-        <v>299</v>
+        <v>380</v>
       </c>
       <c r="E30" t="n">
-        <v>395</v>
+        <v>647</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>45891</v>
+        <v>45894</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D31" t="n">
-        <v>380</v>
+        <v>225.25</v>
       </c>
       <c r="E31" t="n">
-        <v>647</v>
+        <v>314</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>45894</v>
+        <v>45899</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112</v>
+        <v>557</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C32" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D32" t="n">
-        <v>225.25</v>
+        <v>167.43</v>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>464</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>45899</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>557</v>
+        <v>189</v>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="D33" t="n">
-        <v>167.43</v>
+        <v>91.08</v>
       </c>
       <c r="E33" t="n">
-        <v>464</v>
+        <v>427</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>45901</v>
+        <v>45906</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D34" t="n">
-        <v>91.08</v>
+        <v>253.25</v>
       </c>
       <c r="E34" t="n">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>45906</v>
+        <v>45912</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D35" t="n">
-        <v>253.25</v>
+        <v>120.67</v>
       </c>
       <c r="E35" t="n">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>45912</v>
@@ -4936,127 +4936,127 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>139</v>
+        <v>999</v>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D36" t="n">
-        <v>120.67</v>
+        <v>312.5</v>
       </c>
       <c r="E36" t="n">
-        <v>227</v>
+        <v>435</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>999</v>
+        <v>144</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="D37" t="n">
-        <v>312.5</v>
+        <v>178.86</v>
       </c>
       <c r="E37" t="n">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>45916</v>
+        <v>45932</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D38" t="n">
-        <v>178.86</v>
+        <v>116.36</v>
       </c>
       <c r="E38" t="n">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>146</v>
+        <v>777</v>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>467</v>
       </c>
       <c r="D39" t="n">
-        <v>116.36</v>
+        <v>485</v>
       </c>
       <c r="E39" t="n">
-        <v>328</v>
+        <v>968</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>777</v>
+        <v>346</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D40" t="n">
-        <v>485</v>
+        <v>117.45</v>
       </c>
       <c r="E40" t="n">
-        <v>968</v>
+        <v>271</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D41" t="n">
-        <v>117.45</v>
+        <v>935</v>
       </c>
       <c r="E41" t="n">
-        <v>271</v>
+        <v>935</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>45939</v>
+        <v>45942</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="B42" t="n">
         <v>2</v>
@@ -5065,330 +5065,330 @@
         <v>454</v>
       </c>
       <c r="D42" t="n">
-        <v>935</v>
+        <v>836</v>
       </c>
       <c r="E42" t="n">
-        <v>935</v>
+        <v>836</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>45942</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="D43" t="n">
-        <v>836</v>
+        <v>466.5</v>
       </c>
       <c r="E43" t="n">
-        <v>836</v>
+        <v>793</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D44" t="n">
-        <v>466.5</v>
+        <v>164</v>
       </c>
       <c r="E44" t="n">
-        <v>793</v>
+        <v>577</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>45951</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>248</v>
+        <v>119</v>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D45" t="n">
-        <v>164</v>
+        <v>216.5</v>
       </c>
       <c r="E45" t="n">
-        <v>577</v>
+        <v>533</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>45957</v>
+        <v>45963</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
         <v>412</v>
       </c>
       <c r="D46" t="n">
-        <v>216.5</v>
+        <v>163.75</v>
       </c>
       <c r="E46" t="n">
-        <v>533</v>
+        <v>292</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>45963</v>
+        <v>45964</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>48</v>
+        <v>788</v>
       </c>
       <c r="B47" t="n">
         <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D47" t="n">
-        <v>163.75</v>
+        <v>143.75</v>
       </c>
       <c r="E47" t="n">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>45964</v>
+        <v>45968</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>788</v>
+        <v>9</v>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D48" t="n">
-        <v>143.75</v>
+        <v>438</v>
       </c>
       <c r="E48" t="n">
-        <v>337</v>
+        <v>524</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>45968</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>334</v>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D49" t="n">
-        <v>438</v>
+        <v>211.83</v>
       </c>
       <c r="E49" t="n">
-        <v>524</v>
+        <v>339</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>334</v>
+        <v>117</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D50" t="n">
-        <v>211.83</v>
+        <v>297.5</v>
       </c>
       <c r="E50" t="n">
-        <v>339</v>
+        <v>431</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>45975</v>
+        <v>45977</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D51" t="n">
-        <v>297.5</v>
+        <v>269.4</v>
       </c>
       <c r="E51" t="n">
-        <v>431</v>
+        <v>803</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>45977</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>66</v>
+        <v>445</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C52" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D52" t="n">
-        <v>269.4</v>
+        <v>143.22</v>
       </c>
       <c r="E52" t="n">
-        <v>803</v>
+        <v>593</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>445</v>
+        <v>333</v>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D53" t="n">
-        <v>143.22</v>
+        <v>587</v>
       </c>
       <c r="E53" t="n">
-        <v>593</v>
+        <v>816</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="B54" t="n">
         <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D54" t="n">
-        <v>587</v>
+        <v>302</v>
       </c>
       <c r="E54" t="n">
-        <v>816</v>
+        <v>423</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>45981</v>
+        <v>45983</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>168</v>
+        <v>225</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D55" t="n">
-        <v>302</v>
+        <v>775</v>
       </c>
       <c r="E55" t="n">
-        <v>423</v>
+        <v>775</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>45983</v>
+        <v>45988</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D56" t="n">
-        <v>775</v>
+        <v>217.33</v>
       </c>
       <c r="E56" t="n">
-        <v>775</v>
+        <v>483</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>233</v>
+        <v>789</v>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C57" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D57" t="n">
-        <v>217.33</v>
+        <v>185.86</v>
       </c>
       <c r="E57" t="n">
-        <v>483</v>
+        <v>416</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>789</v>
+        <v>223</v>
       </c>
       <c r="B58" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D58" t="n">
-        <v>185.86</v>
+        <v>658.5</v>
       </c>
       <c r="E58" t="n">
-        <v>416</v>
+        <v>1051</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>45992</v>
@@ -5396,59 +5396,59 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>223</v>
+        <v>677</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C59" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D59" t="n">
-        <v>658.5</v>
+        <v>323.75</v>
       </c>
       <c r="E59" t="n">
-        <v>1051</v>
+        <v>718</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>677</v>
+        <v>127</v>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D60" t="n">
-        <v>323.75</v>
+        <v>166.75</v>
       </c>
       <c r="E60" t="n">
-        <v>718</v>
+        <v>506</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>45994</v>
+        <v>45997</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
       <c r="B61" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C61" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D61" t="n">
-        <v>166.75</v>
+        <v>111.5</v>
       </c>
       <c r="E61" t="n">
-        <v>506</v>
+        <v>207</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>45997</v>
@@ -5456,39 +5456,39 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>14</v>
+        <v>367</v>
       </c>
       <c r="B62" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D62" t="n">
-        <v>111.5</v>
+        <v>140</v>
       </c>
       <c r="E62" t="n">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>367</v>
+        <v>88</v>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D63" t="n">
-        <v>140</v>
+        <v>1364</v>
       </c>
       <c r="E63" t="n">
-        <v>256</v>
+        <v>1364</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>45999</v>
@@ -5496,107 +5496,107 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="D64" t="n">
-        <v>1364</v>
+        <v>258.6</v>
       </c>
       <c r="E64" t="n">
-        <v>1364</v>
+        <v>779</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>45999</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
+        <v>344</v>
+      </c>
+      <c r="B65" t="n">
         <v>7</v>
       </c>
-      <c r="B65" t="n">
-        <v>6</v>
-      </c>
       <c r="C65" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D65" t="n">
-        <v>258.6</v>
+        <v>222</v>
       </c>
       <c r="E65" t="n">
-        <v>779</v>
+        <v>656</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>344</v>
+        <v>599</v>
       </c>
       <c r="B66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" t="n">
         <v>310</v>
       </c>
       <c r="D66" t="n">
-        <v>222</v>
+        <v>279.8</v>
       </c>
       <c r="E66" t="n">
-        <v>656</v>
+        <v>384</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C67" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D67" t="n">
-        <v>279.8</v>
+        <v>141.1</v>
       </c>
       <c r="E67" t="n">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>578</v>
+        <v>77</v>
       </c>
       <c r="B68" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D68" t="n">
-        <v>141.1</v>
+        <v>290</v>
       </c>
       <c r="E68" t="n">
-        <v>409</v>
+        <v>771</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46017</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>77</v>
+        <v>336</v>
       </c>
       <c r="B69" t="n">
         <v>6</v>
@@ -5605,50 +5605,50 @@
         <v>294</v>
       </c>
       <c r="D69" t="n">
-        <v>290</v>
+        <v>276.6</v>
       </c>
       <c r="E69" t="n">
-        <v>771</v>
+        <v>842</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>336</v>
+        <v>478</v>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D70" t="n">
-        <v>276.6</v>
+        <v>190.5</v>
       </c>
       <c r="E70" t="n">
-        <v>842</v>
+        <v>302</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>478</v>
+        <v>136</v>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C71" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D71" t="n">
-        <v>190.5</v>
+        <v>123.09</v>
       </c>
       <c r="E71" t="n">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="F71" s="1" t="n">
         <v>46029</v>
@@ -5656,99 +5656,99 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="B72" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D72" t="n">
-        <v>123.09</v>
+        <v>220.5</v>
       </c>
       <c r="E72" t="n">
-        <v>399</v>
+        <v>337</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C73" t="n">
         <v>281</v>
       </c>
       <c r="D73" t="n">
-        <v>220.5</v>
+        <v>171.25</v>
       </c>
       <c r="E73" t="n">
-        <v>337</v>
+        <v>694</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>28</v>
+        <v>355</v>
       </c>
       <c r="B74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C74" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D74" t="n">
-        <v>171.25</v>
+        <v>250.33</v>
       </c>
       <c r="E74" t="n">
-        <v>694</v>
+        <v>469</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46031</v>
+        <v>46033</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>355</v>
+        <v>25</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D75" t="n">
-        <v>250.33</v>
+        <v>112.17</v>
       </c>
       <c r="E75" t="n">
-        <v>469</v>
+        <v>249</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46033</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>25</v>
+        <v>456</v>
       </c>
       <c r="B76" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C76" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D76" t="n">
-        <v>112.17</v>
+        <v>163.22</v>
       </c>
       <c r="E76" t="n">
-        <v>249</v>
+        <v>438</v>
       </c>
       <c r="F76" s="1" t="n">
         <v>46035</v>
@@ -5756,199 +5756,199 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>456</v>
+        <v>18</v>
       </c>
       <c r="B77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77" t="n">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D77" t="n">
-        <v>163.22</v>
+        <v>121.2</v>
       </c>
       <c r="E77" t="n">
-        <v>438</v>
+        <v>310</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>18</v>
+        <v>559</v>
       </c>
       <c r="B78" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C78" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D78" t="n">
-        <v>121.2</v>
+        <v>358</v>
       </c>
       <c r="E78" t="n">
-        <v>310</v>
+        <v>881</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46038</v>
+        <v>46040</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>559</v>
+        <v>44</v>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
         <v>261</v>
       </c>
       <c r="D79" t="n">
-        <v>358</v>
+        <v>347.33</v>
       </c>
       <c r="E79" t="n">
-        <v>881</v>
+        <v>552</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C80" t="n">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D80" t="n">
-        <v>347.33</v>
+        <v>120.91</v>
       </c>
       <c r="E80" t="n">
-        <v>552</v>
+        <v>490</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125</v>
+        <v>567</v>
       </c>
       <c r="B81" t="n">
         <v>12</v>
       </c>
       <c r="C81" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D81" t="n">
-        <v>120.91</v>
+        <v>112.45</v>
       </c>
       <c r="E81" t="n">
-        <v>490</v>
+        <v>555</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>567</v>
+        <v>447</v>
       </c>
       <c r="B82" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C82" t="n">
         <v>250</v>
       </c>
       <c r="D82" t="n">
-        <v>112.45</v>
+        <v>155.33</v>
       </c>
       <c r="E82" t="n">
-        <v>555</v>
+        <v>495</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>447</v>
+        <v>227</v>
       </c>
       <c r="B83" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D83" t="n">
-        <v>155.33</v>
+        <v>938</v>
       </c>
       <c r="E83" t="n">
-        <v>495</v>
+        <v>938</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>227</v>
+        <v>448</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C84" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D84" t="n">
-        <v>938</v>
+        <v>290.2</v>
       </c>
       <c r="E84" t="n">
-        <v>938</v>
+        <v>510</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>448</v>
+        <v>689</v>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D85" t="n">
-        <v>290.2</v>
+        <v>128.73</v>
       </c>
       <c r="E85" t="n">
-        <v>510</v>
+        <v>361</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>689</v>
+        <v>122</v>
       </c>
       <c r="B86" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C86" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D86" t="n">
-        <v>128.73</v>
+        <v>279</v>
       </c>
       <c r="E86" t="n">
-        <v>361</v>
+        <v>759</v>
       </c>
       <c r="F86" s="1" t="n">
         <v>46053</v>
@@ -5956,39 +5956,39 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C87" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D87" t="n">
-        <v>279</v>
+        <v>176.57</v>
       </c>
       <c r="E87" t="n">
-        <v>759</v>
+        <v>570</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>199</v>
+        <v>33</v>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D88" t="n">
-        <v>176.57</v>
+        <v>210.6</v>
       </c>
       <c r="E88" t="n">
-        <v>570</v>
+        <v>645</v>
       </c>
       <c r="F88" s="1" t="n">
         <v>46054</v>
@@ -5996,87 +5996,87 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C89" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D89" t="n">
-        <v>210.6</v>
+        <v>170.57</v>
       </c>
       <c r="E89" t="n">
-        <v>645</v>
+        <v>479</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>46054</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C90" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D90" t="n">
-        <v>170.57</v>
+        <v>280.2</v>
       </c>
       <c r="E90" t="n">
-        <v>479</v>
+        <v>592</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>46057</v>
+        <v>46060</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>236</v>
+        <v>556</v>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D91" t="n">
-        <v>280.2</v>
+        <v>1250</v>
       </c>
       <c r="E91" t="n">
-        <v>592</v>
+        <v>1250</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>46060</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>556</v>
+        <v>266</v>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D92" t="n">
-        <v>1250</v>
+        <v>361.33</v>
       </c>
       <c r="E92" t="n">
-        <v>1250</v>
+        <v>957</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>266</v>
+        <v>4</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
@@ -6085,50 +6085,50 @@
         <v>213</v>
       </c>
       <c r="D93" t="n">
-        <v>361.33</v>
+        <v>426.67</v>
       </c>
       <c r="E93" t="n">
-        <v>957</v>
+        <v>531</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C94" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D94" t="n">
-        <v>426.67</v>
+        <v>139.45</v>
       </c>
       <c r="E94" t="n">
-        <v>531</v>
+        <v>426</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>157</v>
+        <v>245</v>
       </c>
       <c r="B95" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D95" t="n">
-        <v>139.45</v>
+        <v>163.33</v>
       </c>
       <c r="E95" t="n">
-        <v>426</v>
+        <v>498</v>
       </c>
       <c r="F95" s="1" t="n">
         <v>46067</v>
@@ -6136,79 +6136,79 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="B96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C96" t="n">
         <v>206</v>
       </c>
       <c r="D96" t="n">
-        <v>163.33</v>
+        <v>190</v>
       </c>
       <c r="E96" t="n">
-        <v>498</v>
+        <v>700</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c r="B97" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C97" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D97" t="n">
-        <v>190</v>
+        <v>154.83</v>
       </c>
       <c r="E97" t="n">
-        <v>700</v>
+        <v>256</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>166</v>
+        <v>579</v>
       </c>
       <c r="B98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C98" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D98" t="n">
-        <v>154.83</v>
+        <v>223</v>
       </c>
       <c r="E98" t="n">
-        <v>256</v>
+        <v>455</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>46071</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>579</v>
+        <v>488</v>
       </c>
       <c r="B99" t="n">
         <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D99" t="n">
-        <v>223</v>
+        <v>222.43</v>
       </c>
       <c r="E99" t="n">
-        <v>455</v>
+        <v>560</v>
       </c>
       <c r="F99" s="1" t="n">
         <v>46077</v>
@@ -6216,39 +6216,39 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B100" t="n">
         <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D100" t="n">
-        <v>222.43</v>
+        <v>206.71</v>
       </c>
       <c r="E100" t="n">
-        <v>560</v>
+        <v>692</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="B101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C101" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D101" t="n">
-        <v>206.71</v>
+        <v>261.8</v>
       </c>
       <c r="E101" t="n">
-        <v>692</v>
+        <v>623</v>
       </c>
       <c r="F101" s="1" t="n">
         <v>46078</v>
@@ -6256,39 +6256,39 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>479</v>
+        <v>133</v>
       </c>
       <c r="B102" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C102" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D102" t="n">
-        <v>261.8</v>
+        <v>159.88</v>
       </c>
       <c r="E102" t="n">
-        <v>623</v>
+        <v>360</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C103" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D103" t="n">
-        <v>159.88</v>
+        <v>138.3</v>
       </c>
       <c r="E103" t="n">
-        <v>360</v>
+        <v>445</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>46079</v>
@@ -6296,119 +6296,119 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B104" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C104" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D104" t="n">
-        <v>138.3</v>
+        <v>110.92</v>
       </c>
       <c r="E104" t="n">
-        <v>445</v>
+        <v>362</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>46079</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>348</v>
+        <v>458</v>
       </c>
       <c r="B105" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C105" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D105" t="n">
-        <v>110.92</v>
+        <v>156.4</v>
       </c>
       <c r="E105" t="n">
-        <v>362</v>
+        <v>436</v>
       </c>
       <c r="F105" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>458</v>
+        <v>3</v>
       </c>
       <c r="B106" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C106" t="n">
         <v>171</v>
       </c>
       <c r="D106" t="n">
-        <v>156.4</v>
+        <v>186.12</v>
       </c>
       <c r="E106" t="n">
-        <v>436</v>
+        <v>533</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="B107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C107" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D107" t="n">
-        <v>186.12</v>
+        <v>235.5</v>
       </c>
       <c r="E107" t="n">
-        <v>533</v>
+        <v>676</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>268</v>
+        <v>23</v>
       </c>
       <c r="B108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C108" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D108" t="n">
-        <v>235.5</v>
+        <v>168</v>
       </c>
       <c r="E108" t="n">
-        <v>676</v>
+        <v>394</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C109" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D109" t="n">
-        <v>168</v>
+        <v>119.55</v>
       </c>
       <c r="E109" t="n">
-        <v>394</v>
+        <v>271</v>
       </c>
       <c r="F109" s="1" t="n">
         <v>46090</v>
@@ -6416,99 +6416,99 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="B110" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C110" t="n">
         <v>160</v>
       </c>
       <c r="D110" t="n">
-        <v>119.55</v>
+        <v>226.71</v>
       </c>
       <c r="E110" t="n">
-        <v>271</v>
+        <v>729</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>99</v>
+        <v>388</v>
       </c>
       <c r="B111" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C111" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D111" t="n">
-        <v>226.71</v>
+        <v>358.5</v>
       </c>
       <c r="E111" t="n">
-        <v>729</v>
+        <v>1126</v>
       </c>
       <c r="F111" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>388</v>
+        <v>257</v>
       </c>
       <c r="B112" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C112" t="n">
         <v>157</v>
       </c>
       <c r="D112" t="n">
-        <v>358.5</v>
+        <v>131.75</v>
       </c>
       <c r="E112" t="n">
-        <v>1126</v>
+        <v>388</v>
       </c>
       <c r="F112" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B113" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C113" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D113" t="n">
-        <v>131.75</v>
+        <v>107.29</v>
       </c>
       <c r="E113" t="n">
-        <v>388</v>
+        <v>245</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>46093</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B114" t="n">
         <v>15</v>
       </c>
       <c r="C114" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D114" t="n">
-        <v>107.29</v>
+        <v>107.93</v>
       </c>
       <c r="E114" t="n">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="F114" s="1" t="n">
         <v>46095</v>
@@ -6516,79 +6516,79 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="B115" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C115" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D115" t="n">
-        <v>107.93</v>
+        <v>162.88</v>
       </c>
       <c r="E115" t="n">
-        <v>210</v>
+        <v>544</v>
       </c>
       <c r="F115" s="1" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>12</v>
+        <v>668</v>
       </c>
       <c r="B116" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C116" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D116" t="n">
-        <v>162.88</v>
+        <v>96</v>
       </c>
       <c r="E116" t="n">
-        <v>544</v>
+        <v>115</v>
       </c>
       <c r="F116" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C117" t="n">
         <v>141</v>
       </c>
       <c r="D117" t="n">
-        <v>96</v>
+        <v>236.83</v>
       </c>
       <c r="E117" t="n">
-        <v>115</v>
+        <v>461</v>
       </c>
       <c r="F117" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>688</v>
+        <v>337</v>
       </c>
       <c r="B118" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C118" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D118" t="n">
-        <v>236.83</v>
+        <v>326.75</v>
       </c>
       <c r="E118" t="n">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F118" s="1" t="n">
         <v>46101</v>
@@ -6596,79 +6596,79 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="B119" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C119" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D119" t="n">
-        <v>326.75</v>
+        <v>204.71</v>
       </c>
       <c r="E119" t="n">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>59</v>
+        <v>678</v>
       </c>
       <c r="B120" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C120" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D120" t="n">
-        <v>204.71</v>
+        <v>121.25</v>
       </c>
       <c r="E120" t="n">
-        <v>492</v>
+        <v>321</v>
       </c>
       <c r="F120" s="1" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>678</v>
+        <v>38</v>
       </c>
       <c r="B121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C121" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D121" t="n">
-        <v>121.25</v>
+        <v>130.73</v>
       </c>
       <c r="E121" t="n">
-        <v>321</v>
+        <v>467</v>
       </c>
       <c r="F121" s="1" t="n">
-        <v>46103</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>38</v>
+        <v>589</v>
       </c>
       <c r="B122" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C122" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D122" t="n">
-        <v>130.73</v>
+        <v>243.83</v>
       </c>
       <c r="E122" t="n">
-        <v>467</v>
+        <v>546</v>
       </c>
       <c r="F122" s="1" t="n">
         <v>46104</v>
@@ -6676,59 +6676,59 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>589</v>
+        <v>228</v>
       </c>
       <c r="B123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C123" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D123" t="n">
-        <v>243.83</v>
+        <v>277</v>
       </c>
       <c r="E123" t="n">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F123" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="B124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C124" t="n">
         <v>131</v>
       </c>
       <c r="D124" t="n">
-        <v>277</v>
+        <v>225.83</v>
       </c>
       <c r="E124" t="n">
-        <v>536</v>
+        <v>474</v>
       </c>
       <c r="F124" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="B125" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D125" t="n">
-        <v>225.83</v>
+        <v>489.67</v>
       </c>
       <c r="E125" t="n">
-        <v>474</v>
+        <v>714</v>
       </c>
       <c r="F125" s="1" t="n">
         <v>46106</v>
@@ -6736,79 +6736,79 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="B126" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C126" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D126" t="n">
-        <v>489.67</v>
+        <v>131.09</v>
       </c>
       <c r="E126" t="n">
-        <v>714</v>
+        <v>257</v>
       </c>
       <c r="F126" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>89</v>
+        <v>259</v>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C127" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D127" t="n">
-        <v>131.09</v>
+        <v>160</v>
       </c>
       <c r="E127" t="n">
-        <v>257</v>
+        <v>502</v>
       </c>
       <c r="F127" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>259</v>
+        <v>455</v>
       </c>
       <c r="B128" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D128" t="n">
-        <v>160</v>
+        <v>280.8</v>
       </c>
       <c r="E128" t="n">
-        <v>502</v>
+        <v>448</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>455</v>
+        <v>339</v>
       </c>
       <c r="B129" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C129" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D129" t="n">
-        <v>280.8</v>
+        <v>1368</v>
       </c>
       <c r="E129" t="n">
-        <v>448</v>
+        <v>1368</v>
       </c>
       <c r="F129" s="1" t="n">
         <v>46110</v>
@@ -6816,47 +6816,47 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C130" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D130" t="n">
-        <v>1368</v>
+        <v>110.09</v>
       </c>
       <c r="E130" t="n">
-        <v>1368</v>
+        <v>266</v>
       </c>
       <c r="F130" s="1" t="n">
-        <v>46110</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>457</v>
+        <v>34</v>
       </c>
       <c r="B131" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C131" t="n">
         <v>115</v>
       </c>
       <c r="D131" t="n">
-        <v>110.09</v>
+        <v>352</v>
       </c>
       <c r="E131" t="n">
-        <v>266</v>
+        <v>704</v>
       </c>
       <c r="F131" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>34</v>
+        <v>277</v>
       </c>
       <c r="B132" t="n">
         <v>5</v>
@@ -6865,30 +6865,30 @@
         <v>113</v>
       </c>
       <c r="D132" t="n">
-        <v>352</v>
+        <v>405.75</v>
       </c>
       <c r="E132" t="n">
-        <v>704</v>
+        <v>986</v>
       </c>
       <c r="F132" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="B133" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D133" t="n">
-        <v>405.75</v>
+        <v>442.33</v>
       </c>
       <c r="E133" t="n">
-        <v>986</v>
+        <v>776</v>
       </c>
       <c r="F133" s="1" t="n">
         <v>46115</v>
@@ -6896,99 +6896,99 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>255</v>
+        <v>36</v>
       </c>
       <c r="B134" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D134" t="n">
-        <v>442.33</v>
+        <v>100.4</v>
       </c>
       <c r="E134" t="n">
-        <v>776</v>
+        <v>309</v>
       </c>
       <c r="F134" s="1" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B135" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C135" t="n">
         <v>107</v>
       </c>
       <c r="D135" t="n">
-        <v>100.4</v>
+        <v>237.67</v>
       </c>
       <c r="E135" t="n">
-        <v>309</v>
+        <v>549</v>
       </c>
       <c r="F135" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B136" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C136" t="n">
         <v>105</v>
       </c>
       <c r="D136" t="n">
-        <v>237.67</v>
+        <v>131.45</v>
       </c>
       <c r="E136" t="n">
-        <v>549</v>
+        <v>317</v>
       </c>
       <c r="F136" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C137" t="n">
         <v>103</v>
       </c>
       <c r="D137" t="n">
-        <v>131.45</v>
+        <v>124.77</v>
       </c>
       <c r="E137" t="n">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="F137" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B138" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C138" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D138" t="n">
-        <v>124.77</v>
+        <v>385.33</v>
       </c>
       <c r="E138" t="n">
-        <v>363</v>
+        <v>1014</v>
       </c>
       <c r="F138" s="1" t="n">
         <v>46120</v>
@@ -6996,79 +6996,79 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>24</v>
+        <v>235</v>
       </c>
       <c r="B139" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C139" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D139" t="n">
-        <v>385.33</v>
+        <v>102.7</v>
       </c>
       <c r="E139" t="n">
-        <v>1014</v>
+        <v>185</v>
       </c>
       <c r="F139" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>235</v>
+        <v>469</v>
       </c>
       <c r="B140" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C140" t="n">
         <v>99</v>
       </c>
       <c r="D140" t="n">
-        <v>102.7</v>
+        <v>105</v>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>311</v>
       </c>
       <c r="F140" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>469</v>
+        <v>778</v>
       </c>
       <c r="B141" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C141" t="n">
         <v>97</v>
       </c>
       <c r="D141" t="n">
-        <v>105</v>
+        <v>350</v>
       </c>
       <c r="E141" t="n">
-        <v>311</v>
+        <v>593</v>
       </c>
       <c r="F141" s="1" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>778</v>
+        <v>889</v>
       </c>
       <c r="B142" t="n">
         <v>4</v>
       </c>
       <c r="C142" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D142" t="n">
-        <v>350</v>
+        <v>527.67</v>
       </c>
       <c r="E142" t="n">
-        <v>593</v>
+        <v>1098</v>
       </c>
       <c r="F142" s="1" t="n">
         <v>46123</v>
@@ -7076,39 +7076,39 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>889</v>
+        <v>368</v>
       </c>
       <c r="B143" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C143" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D143" t="n">
-        <v>527.67</v>
+        <v>179.44</v>
       </c>
       <c r="E143" t="n">
-        <v>1098</v>
+        <v>682</v>
       </c>
       <c r="F143" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>368</v>
+        <v>278</v>
       </c>
       <c r="B144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C144" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D144" t="n">
-        <v>179.44</v>
+        <v>204.5</v>
       </c>
       <c r="E144" t="n">
-        <v>682</v>
+        <v>570</v>
       </c>
       <c r="F144" s="1" t="n">
         <v>46124</v>
@@ -7116,107 +7116,107 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>278</v>
+        <v>57</v>
       </c>
       <c r="B145" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C145" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D145" t="n">
-        <v>204.5</v>
+        <v>134.75</v>
       </c>
       <c r="E145" t="n">
-        <v>570</v>
+        <v>684</v>
       </c>
       <c r="F145" s="1" t="n">
-        <v>46124</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>49</v>
+        <v>289</v>
       </c>
       <c r="B146" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C146" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D146" t="n">
-        <v>123.62</v>
+        <v>180.44</v>
       </c>
       <c r="E146" t="n">
-        <v>238</v>
+        <v>632</v>
       </c>
       <c r="F146" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>57</v>
+        <v>258</v>
       </c>
       <c r="B147" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C147" t="n">
         <v>89</v>
       </c>
       <c r="D147" t="n">
-        <v>134.75</v>
+        <v>160.2</v>
       </c>
       <c r="E147" t="n">
-        <v>684</v>
+        <v>348</v>
       </c>
       <c r="F147" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>289</v>
+        <v>29</v>
       </c>
       <c r="B148" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C148" t="n">
         <v>88</v>
       </c>
       <c r="D148" t="n">
-        <v>180.44</v>
+        <v>236.29</v>
       </c>
       <c r="E148" t="n">
-        <v>632</v>
+        <v>568</v>
       </c>
       <c r="F148" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>258</v>
+        <v>79</v>
       </c>
       <c r="B149" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C149" t="n">
         <v>87</v>
       </c>
       <c r="D149" t="n">
-        <v>160.2</v>
+        <v>322.2</v>
       </c>
       <c r="E149" t="n">
-        <v>348</v>
+        <v>773</v>
       </c>
       <c r="F149" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B150" t="n">
         <v>8</v>
@@ -7225,298 +7225,298 @@
         <v>86</v>
       </c>
       <c r="D150" t="n">
-        <v>236.29</v>
+        <v>212</v>
       </c>
       <c r="E150" t="n">
-        <v>568</v>
+        <v>526</v>
       </c>
       <c r="F150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="B151" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C151" t="n">
         <v>85</v>
       </c>
       <c r="D151" t="n">
-        <v>322.2</v>
+        <v>128.67</v>
       </c>
       <c r="E151" t="n">
-        <v>773</v>
+        <v>296</v>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>13</v>
+        <v>246</v>
       </c>
       <c r="B152" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C152" t="n">
         <v>84</v>
       </c>
       <c r="D152" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E152" t="n">
-        <v>526</v>
+        <v>717</v>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>269</v>
+        <v>22</v>
       </c>
       <c r="B153" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D153" t="n">
-        <v>128.67</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>246</v>
+        <v>58</v>
       </c>
       <c r="B154" t="n">
         <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D154" t="n">
-        <v>208</v>
+        <v>187.38</v>
       </c>
       <c r="E154" t="n">
-        <v>717</v>
+        <v>511</v>
       </c>
       <c r="F154" s="1" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>22</v>
+        <v>378</v>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C155" t="n">
         <v>80</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>255.6</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>58</v>
+        <v>279</v>
       </c>
       <c r="B156" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C156" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D156" t="n">
-        <v>187.38</v>
+        <v>164.43</v>
       </c>
       <c r="E156" t="n">
-        <v>511</v>
+        <v>470</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>378</v>
+        <v>238</v>
       </c>
       <c r="B157" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C157" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D157" t="n">
-        <v>255.6</v>
+        <v>111.46</v>
       </c>
       <c r="E157" t="n">
-        <v>742</v>
+        <v>520</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46131</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>279</v>
+        <v>568</v>
       </c>
       <c r="B158" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C158" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D158" t="n">
-        <v>164.43</v>
+        <v>103.75</v>
       </c>
       <c r="E158" t="n">
-        <v>470</v>
+        <v>275</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>238</v>
+        <v>569</v>
       </c>
       <c r="B159" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C159" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D159" t="n">
-        <v>111.46</v>
+        <v>173.22</v>
       </c>
       <c r="E159" t="n">
-        <v>520</v>
+        <v>582</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>568</v>
+        <v>17</v>
       </c>
       <c r="B160" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C160" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D160" t="n">
-        <v>103.75</v>
+        <v>233.29</v>
       </c>
       <c r="E160" t="n">
-        <v>275</v>
+        <v>741</v>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>569</v>
+        <v>349</v>
       </c>
       <c r="B161" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C161" t="n">
         <v>71</v>
       </c>
       <c r="D161" t="n">
-        <v>173.22</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>582</v>
+        <v>303</v>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="B162" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C162" t="n">
         <v>70</v>
       </c>
       <c r="D162" t="n">
-        <v>233.29</v>
+        <v>232.6</v>
       </c>
       <c r="E162" t="n">
-        <v>741</v>
+        <v>514</v>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>349</v>
+        <v>124</v>
       </c>
       <c r="B163" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C163" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D163" t="n">
-        <v>93.23999999999999</v>
+        <v>131.82</v>
       </c>
       <c r="E163" t="n">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>226</v>
+        <v>35</v>
       </c>
       <c r="B164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C164" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D164" t="n">
-        <v>232.6</v>
+        <v>209.25</v>
       </c>
       <c r="E164" t="n">
-        <v>514</v>
+        <v>742</v>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>124</v>
+        <v>357</v>
       </c>
       <c r="B165" t="n">
         <v>12</v>
@@ -7525,658 +7525,658 @@
         <v>65</v>
       </c>
       <c r="D165" t="n">
-        <v>131.82</v>
+        <v>140.64</v>
       </c>
       <c r="E165" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="B166" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C166" t="n">
         <v>64</v>
       </c>
       <c r="D166" t="n">
-        <v>209.25</v>
+        <v>201</v>
       </c>
       <c r="E166" t="n">
-        <v>742</v>
+        <v>772</v>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>357</v>
+        <v>129</v>
       </c>
       <c r="B167" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C167" t="n">
         <v>63</v>
       </c>
       <c r="D167" t="n">
-        <v>140.64</v>
+        <v>147.5</v>
       </c>
       <c r="E167" t="n">
-        <v>240</v>
+        <v>399</v>
       </c>
       <c r="F167" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="B168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C168" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D168" t="n">
-        <v>201</v>
+        <v>334.6</v>
       </c>
       <c r="E168" t="n">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F168" s="1" t="n">
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="B169" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C169" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D169" t="n">
-        <v>147.5</v>
+        <v>206.6</v>
       </c>
       <c r="E169" t="n">
-        <v>399</v>
+        <v>464</v>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>377</v>
+        <v>237</v>
       </c>
       <c r="B170" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C170" t="n">
         <v>56</v>
       </c>
       <c r="D170" t="n">
-        <v>334.6</v>
+        <v>121.64</v>
       </c>
       <c r="E170" t="n">
-        <v>784</v>
+        <v>214</v>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>177</v>
+        <v>345</v>
       </c>
       <c r="B171" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C171" t="n">
         <v>55</v>
       </c>
       <c r="D171" t="n">
-        <v>206.6</v>
+        <v>115.25</v>
       </c>
       <c r="E171" t="n">
-        <v>464</v>
+        <v>365</v>
       </c>
       <c r="F171" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="B172" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C172" t="n">
         <v>54</v>
       </c>
       <c r="D172" t="n">
-        <v>121.64</v>
+        <v>234.71</v>
       </c>
       <c r="E172" t="n">
-        <v>214</v>
+        <v>547</v>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>345</v>
+        <v>45</v>
       </c>
       <c r="B173" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C173" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D173" t="n">
-        <v>115.25</v>
+        <v>261.5</v>
       </c>
       <c r="E173" t="n">
-        <v>365</v>
+        <v>441</v>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46144</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>137</v>
+        <v>267</v>
       </c>
       <c r="B174" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C174" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D174" t="n">
-        <v>234.71</v>
+        <v>286.8</v>
       </c>
       <c r="E174" t="n">
-        <v>547</v>
+        <v>804</v>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="B175" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C175" t="n">
         <v>50</v>
       </c>
       <c r="D175" t="n">
-        <v>261.5</v>
+        <v>174.44</v>
       </c>
       <c r="E175" t="n">
-        <v>441</v>
+        <v>550</v>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>267</v>
+        <v>67</v>
       </c>
       <c r="B176" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C176" t="n">
         <v>49</v>
       </c>
       <c r="D176" t="n">
-        <v>286.8</v>
+        <v>115.64</v>
       </c>
       <c r="E176" t="n">
-        <v>804</v>
+        <v>303</v>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B177" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C177" t="n">
         <v>48</v>
       </c>
       <c r="D177" t="n">
-        <v>174.44</v>
+        <v>112.85</v>
       </c>
       <c r="E177" t="n">
-        <v>550</v>
+        <v>451</v>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="B178" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C178" t="n">
         <v>47</v>
       </c>
       <c r="D178" t="n">
-        <v>115.64</v>
+        <v>131.08</v>
       </c>
       <c r="E178" t="n">
-        <v>303</v>
+        <v>541</v>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="B179" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D179" t="n">
-        <v>112.85</v>
+        <v>113.87</v>
       </c>
       <c r="E179" t="n">
-        <v>451</v>
+        <v>307</v>
       </c>
       <c r="F179" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>15</v>
+        <v>459</v>
       </c>
       <c r="B180" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C180" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D180" t="n">
-        <v>131.08</v>
+        <v>107.5</v>
       </c>
       <c r="E180" t="n">
-        <v>541</v>
+        <v>427</v>
       </c>
       <c r="F180" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="B181" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C181" t="n">
         <v>43</v>
       </c>
       <c r="D181" t="n">
-        <v>113.87</v>
+        <v>276.33</v>
       </c>
       <c r="E181" t="n">
-        <v>307</v>
+        <v>779</v>
       </c>
       <c r="F181" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>459</v>
+        <v>147</v>
       </c>
       <c r="B182" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C182" t="n">
         <v>42</v>
       </c>
       <c r="D182" t="n">
-        <v>107.5</v>
+        <v>120.36</v>
       </c>
       <c r="E182" t="n">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>288</v>
+        <v>145</v>
       </c>
       <c r="B183" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C183" t="n">
         <v>41</v>
       </c>
       <c r="D183" t="n">
-        <v>276.33</v>
+        <v>191.29</v>
       </c>
       <c r="E183" t="n">
-        <v>779</v>
+        <v>336</v>
       </c>
       <c r="F183" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>147</v>
+        <v>338</v>
       </c>
       <c r="B184" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C184" t="n">
         <v>40</v>
       </c>
       <c r="D184" t="n">
-        <v>120.36</v>
+        <v>106.43</v>
       </c>
       <c r="E184" t="n">
-        <v>359</v>
+        <v>190</v>
       </c>
       <c r="F184" s="1" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="B185" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D185" t="n">
-        <v>191.29</v>
+        <v>99.8</v>
       </c>
       <c r="E185" t="n">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>338</v>
+        <v>249</v>
       </c>
       <c r="B186" t="n">
         <v>8</v>
       </c>
       <c r="C186" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D186" t="n">
-        <v>106.43</v>
+        <v>195.29</v>
       </c>
       <c r="E186" t="n">
-        <v>190</v>
+        <v>779</v>
       </c>
       <c r="F186" s="1" t="n">
-        <v>46151</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>239</v>
+        <v>577</v>
       </c>
       <c r="B187" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C187" t="n">
         <v>36</v>
       </c>
       <c r="D187" t="n">
-        <v>99.8</v>
+        <v>233</v>
       </c>
       <c r="E187" t="n">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="B188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C188" t="n">
         <v>35</v>
       </c>
       <c r="D188" t="n">
-        <v>195.29</v>
+        <v>214.62</v>
       </c>
       <c r="E188" t="n">
-        <v>779</v>
+        <v>365</v>
       </c>
       <c r="F188" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>577</v>
+        <v>466</v>
       </c>
       <c r="B189" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C189" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D189" t="n">
-        <v>233</v>
+        <v>182.88</v>
       </c>
       <c r="E189" t="n">
-        <v>281</v>
+        <v>326</v>
       </c>
       <c r="F189" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>149</v>
+        <v>379</v>
       </c>
       <c r="B190" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C190" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D190" t="n">
-        <v>214.62</v>
+        <v>127</v>
       </c>
       <c r="E190" t="n">
-        <v>365</v>
+        <v>455</v>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B191" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C191" t="n">
         <v>31</v>
       </c>
       <c r="D191" t="n">
-        <v>182.88</v>
+        <v>147.3</v>
       </c>
       <c r="E191" t="n">
-        <v>326</v>
+        <v>506</v>
       </c>
       <c r="F191" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>379</v>
+        <v>78</v>
       </c>
       <c r="B192" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C192" t="n">
         <v>30</v>
       </c>
       <c r="D192" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E192" t="n">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="F192" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>467</v>
+        <v>358</v>
       </c>
       <c r="B193" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C193" t="n">
         <v>29</v>
       </c>
       <c r="D193" t="n">
-        <v>147.3</v>
+        <v>360</v>
       </c>
       <c r="E193" t="n">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="B194" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194" t="n">
         <v>28</v>
       </c>
       <c r="D194" t="n">
-        <v>119</v>
+        <v>133.5</v>
       </c>
       <c r="E194" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F194" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>358</v>
+        <v>468</v>
       </c>
       <c r="B195" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C195" t="n">
         <v>27</v>
       </c>
       <c r="D195" t="n">
-        <v>360</v>
+        <v>112.8</v>
       </c>
       <c r="E195" t="n">
-        <v>483</v>
+        <v>331</v>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>369</v>
+        <v>159</v>
       </c>
       <c r="B196" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C196" t="n">
         <v>26</v>
       </c>
       <c r="D196" t="n">
-        <v>133.5</v>
+        <v>182.12</v>
       </c>
       <c r="E196" t="n">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="F196" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>468</v>
+        <v>366</v>
       </c>
       <c r="B197" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C197" t="n">
         <v>25</v>
       </c>
       <c r="D197" t="n">
-        <v>112.8</v>
+        <v>248</v>
       </c>
       <c r="E197" t="n">
-        <v>331</v>
+        <v>658</v>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B198" t="n">
         <v>9</v>
@@ -8185,473 +8185,473 @@
         <v>24</v>
       </c>
       <c r="D198" t="n">
-        <v>182.12</v>
+        <v>199.12</v>
       </c>
       <c r="E198" t="n">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="B199" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C199" t="n">
         <v>23</v>
       </c>
       <c r="D199" t="n">
-        <v>248</v>
+        <v>452</v>
       </c>
       <c r="E199" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F199" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>178</v>
+        <v>389</v>
       </c>
       <c r="B200" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C200" t="n">
         <v>22</v>
       </c>
       <c r="D200" t="n">
-        <v>199.12</v>
+        <v>134.5</v>
       </c>
       <c r="E200" t="n">
-        <v>441</v>
+        <v>490</v>
       </c>
       <c r="F200" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>399</v>
+        <v>26</v>
       </c>
       <c r="B201" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C201" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D201" t="n">
-        <v>452</v>
+        <v>135</v>
       </c>
       <c r="E201" t="n">
-        <v>661</v>
+        <v>403</v>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>389</v>
+        <v>115</v>
       </c>
       <c r="B202" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C202" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D202" t="n">
-        <v>134.5</v>
+        <v>245</v>
       </c>
       <c r="E202" t="n">
-        <v>490</v>
+        <v>518</v>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>26</v>
+        <v>588</v>
       </c>
       <c r="B203" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C203" t="n">
         <v>18</v>
       </c>
       <c r="D203" t="n">
-        <v>135</v>
+        <v>355.67</v>
       </c>
       <c r="E203" t="n">
-        <v>403</v>
+        <v>620</v>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>115</v>
+        <v>799</v>
       </c>
       <c r="B204" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C204" t="n">
         <v>17</v>
       </c>
       <c r="D204" t="n">
-        <v>245</v>
+        <v>146.1</v>
       </c>
       <c r="E204" t="n">
-        <v>518</v>
+        <v>372</v>
       </c>
       <c r="F204" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>588</v>
+        <v>299</v>
       </c>
       <c r="B205" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C205" t="n">
         <v>16</v>
       </c>
       <c r="D205" t="n">
-        <v>355.67</v>
+        <v>228.83</v>
       </c>
       <c r="E205" t="n">
-        <v>620</v>
+        <v>499</v>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>799</v>
+        <v>113</v>
       </c>
       <c r="B206" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C206" t="n">
         <v>15</v>
       </c>
       <c r="D206" t="n">
-        <v>146.1</v>
+        <v>169.33</v>
       </c>
       <c r="E206" t="n">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="F206" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>299</v>
+        <v>669</v>
       </c>
       <c r="B207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C207" t="n">
         <v>14</v>
       </c>
       <c r="D207" t="n">
-        <v>228.83</v>
+        <v>313.8</v>
       </c>
       <c r="E207" t="n">
-        <v>499</v>
+        <v>608</v>
       </c>
       <c r="F207" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B208" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C208" t="n">
         <v>13</v>
       </c>
       <c r="D208" t="n">
-        <v>169.33</v>
+        <v>172</v>
       </c>
       <c r="E208" t="n">
-        <v>300</v>
+        <v>349</v>
       </c>
       <c r="F208" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>669</v>
+        <v>138</v>
       </c>
       <c r="B209" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C209" t="n">
         <v>12</v>
       </c>
       <c r="D209" t="n">
-        <v>313.8</v>
+        <v>109.93</v>
       </c>
       <c r="E209" t="n">
-        <v>608</v>
+        <v>724</v>
       </c>
       <c r="F209" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="B210" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C210" t="n">
         <v>11</v>
       </c>
       <c r="D210" t="n">
-        <v>172</v>
+        <v>429</v>
       </c>
       <c r="E210" t="n">
-        <v>349</v>
+        <v>742</v>
       </c>
       <c r="F210" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B211" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C211" t="n">
         <v>10</v>
       </c>
       <c r="D211" t="n">
-        <v>109.93</v>
+        <v>88.42</v>
       </c>
       <c r="E211" t="n">
-        <v>724</v>
+        <v>311</v>
       </c>
       <c r="F211" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B212" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C212" t="n">
         <v>9</v>
       </c>
       <c r="D212" t="n">
-        <v>429</v>
+        <v>236.67</v>
       </c>
       <c r="E212" t="n">
-        <v>742</v>
+        <v>652</v>
       </c>
       <c r="F212" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>148</v>
+        <v>679</v>
       </c>
       <c r="B213" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C213" t="n">
         <v>8</v>
       </c>
       <c r="D213" t="n">
-        <v>88.42</v>
+        <v>233.43</v>
       </c>
       <c r="E213" t="n">
-        <v>311</v>
+        <v>593</v>
       </c>
       <c r="F213" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B214" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C214" t="n">
         <v>7</v>
       </c>
       <c r="D214" t="n">
-        <v>236.67</v>
+        <v>113.93</v>
       </c>
       <c r="E214" t="n">
-        <v>652</v>
+        <v>306</v>
       </c>
       <c r="F214" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>679</v>
+        <v>37</v>
       </c>
       <c r="B215" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C215" t="n">
         <v>6</v>
       </c>
       <c r="D215" t="n">
-        <v>233.43</v>
+        <v>126.77</v>
       </c>
       <c r="E215" t="n">
-        <v>593</v>
+        <v>336</v>
       </c>
       <c r="F215" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B216" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C216" t="n">
         <v>5</v>
       </c>
       <c r="D216" t="n">
-        <v>113.93</v>
+        <v>208.88</v>
       </c>
       <c r="E216" t="n">
-        <v>306</v>
+        <v>408</v>
       </c>
       <c r="F216" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>37</v>
+        <v>558</v>
       </c>
       <c r="B217" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C217" t="n">
         <v>4</v>
       </c>
       <c r="D217" t="n">
-        <v>126.77</v>
+        <v>430.67</v>
       </c>
       <c r="E217" t="n">
-        <v>336</v>
+        <v>570</v>
       </c>
       <c r="F217" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="B218" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C218" t="n">
         <v>3</v>
       </c>
       <c r="D218" t="n">
-        <v>208.88</v>
+        <v>154.18</v>
       </c>
       <c r="E218" t="n">
-        <v>408</v>
+        <v>538</v>
       </c>
       <c r="F218" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>558</v>
+        <v>156</v>
       </c>
       <c r="B219" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C219" t="n">
         <v>2</v>
       </c>
       <c r="D219" t="n">
-        <v>430.67</v>
+        <v>155.91</v>
       </c>
       <c r="E219" t="n">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="F219" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="B220" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>154.18</v>
+        <v>121.36</v>
       </c>
       <c r="E220" t="n">
-        <v>538</v>
+        <v>238</v>
       </c>
       <c r="F220" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="B221" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>155.91</v>
+        <v>243.14</v>
       </c>
       <c r="E221" t="n">
-        <v>551</v>
+        <v>687</v>
       </c>
       <c r="F221" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
   </sheetData>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
         <v>63</v>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -8922,15 +8922,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B32" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B33" t="n">
         <v>49</v>
@@ -8938,7 +8938,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B34" t="n">
         <v>49</v>
@@ -9029,7 +9029,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
@@ -9228,15 +9228,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B13" t="n">
         <v>57</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B14" t="n">
         <v>57</v>
@@ -9276,7 +9276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B18" t="n">
         <v>54</v>
@@ -9284,23 +9284,23 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B19" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="B20" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n">
         <v>53</v>
@@ -9308,7 +9308,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B22" t="n">
         <v>53</v>
@@ -9316,7 +9316,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B23" t="n">
         <v>53</v>
